--- a/outputs/evaluation/decision/v2/CF_M08/run_2/CF_M08_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M08/run_2/CF_M08_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2857</v>
+        <v>0.625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1667</v>
+        <v>0.3571</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9235</v>
+        <v>0.8472</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1667</v>
+        <v>0.0667</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.9714</v>
       </c>
     </row>
     <row r="8">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2857</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1667</v>
+        <v>0.3571</v>
       </c>
     </row>
     <row r="9">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -752,31 +752,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
         <v>7</v>
       </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4</v>
-      </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -789,34 +789,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
         <v>7</v>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,28 +974,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AD12</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.847</v>
+        <v>0.7936</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1009,72 +1009,72 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Traefik acts as a reverse proxy and load balancer, improving the availability and responsiveness of the application.</t>
+          <t>Prisma is an ORM tool used to simplify database access and management.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>C_04, C_08</t>
+          <t>C_05</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_02, AU_05</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
+          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M08_C08, *CF_M08_C09</t>
+          <t>*CF_M08_C24</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU09</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M08_AD03</t>
+          <t>CF_M08_AD13</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0.8315</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -1088,58 +1088,314 @@
         </is>
       </c>
       <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is used generally to manage shared resources, such as configurations, logs or database connections, where having multiple instances could lead to inconsistent states or inefficient use of resources.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>It is generally used for manage shared resources, such as configurations, records or connections to databases data, where having multiple instances could lead to inconsistent states or usage resource inefficient.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>CF_M08_C06</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CF_M08_P05</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CF_M08_AD14</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8476</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.9946</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>C_02, C_05</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>*CF_M08_C21, CF_M08_C05</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>CF_M08_P03</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CF_M08_AD02</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8752</v>
+      </c>
+      <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>C_03</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Traefik opens port 443 to handle HTTPS traffic, which is the standard for secure communications on the web. HTTPS encrypts the data transmitted between clients and the server, protecting the integrity and confidentiality of the information.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>R_20, C_03</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>AU_02, AU_24</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>*CF_M08_C11, *CF_M08_C12</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>CF_M08_AU22</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
+directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>*CF_M08_C10</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CF_M08_AU03</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CF_M08_AD01</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8881</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Traefik acts as a reverse proxy and load balancer, distributing traffic between multiple instances of a service, improving the availability and responsiveness of the application.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>R_22, C_04</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>AU_02, AU_05</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>CF_M08_C08, *CF_M08_C09</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CF_M08_AU03</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
         <v>43</v>
       </c>
     </row>
@@ -1154,7 +1410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1207,7 +1463,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_07</t>
+          <t>R_28, C_07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1222,151 +1478,81 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6187</v>
+        <v>0.6722</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that offers additional structure, features, and optimizations that allow building applications faster and without the need to configure tools manually.</t>
+          <t>The Observer pattern establishes a one-to-many relationship between objects... When the subject's state changes, it automatically notifies all its observers, allowing them to react appropriately.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_02, C_06</t>
+          <t>C_05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7467</v>
+        <v>0.6006</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This approach promotes modularity, code reuse, and maintainability, facilitating the management of the application.</t>
+          <t>Docker is a containerization platform used to manage the execution of the application services.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_05</t>
+          <t>C_05, C_06</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M08_AD10</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.7407</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is used generally to manage shared resources, such as configurations, logs, or database connections, where having multiple instances could lead to inconsistent states or inefficient use of resources.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C_04, Performance</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CF_M08_AD10</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0.6389</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AD_07</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Docker is used to create an application and package it together with its dependencies and libraries in a container, allowing to develop locally, raise a database, and build an image that can be deployed in different environments.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>C_05, C_06</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CF_M08_AD07</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.6415</v>
+        <v>0.6791</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1423,23 +1609,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M08_AD02</t>
+          <t>CF_M08_AD03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
-directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
+          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>*CF_M08_C10</t>
+          <t>*CF_M08_C11, *CF_M08_C12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1451,7 +1636,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.757</v>
+        <v>0.8749</v>
       </c>
     </row>
     <row r="3">
@@ -1480,11 +1665,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.6589</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="4">
@@ -1517,7 +1702,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.7467</v>
+        <v>0.5822000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1546,11 +1731,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.7212</v>
+        <v>0.6473</v>
       </c>
     </row>
     <row r="6">
@@ -1579,11 +1764,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.7174</v>
+        <v>0.7005</v>
       </c>
     </row>
     <row r="7">
@@ -1616,7 +1801,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.6631</v>
+        <v>0.6881</v>
       </c>
     </row>
     <row r="8">
@@ -1649,7 +1834,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.7241</v>
+        <v>0.7336</v>
       </c>
     </row>
     <row r="9">
@@ -1678,11 +1863,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.7407</v>
+        <v>0.7812</v>
       </c>
     </row>
     <row r="10">
@@ -1715,40 +1900,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.5719</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M08_AD12</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>*CF_M08_C24</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CF_M08_AU09</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AD_07</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0.5989</v>
+        <v>0.7723</v>
       </c>
     </row>
   </sheetData>
